--- a/Extracted_data_analysis/polar/Output-Transformed_data/summary_split_counts_question_4.xlsx
+++ b/Extracted_data_analysis/polar/Output-Transformed_data/summary_split_counts_question_4.xlsx
@@ -17,7 +17,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+  <si>
+    <t xml:space="preserve">LaudienOrchard_2012_significance_depth_substratum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HamadaEtAl_1986_Observation_marine_benthic.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnsellEtAl_1998_Swimming_Antarctic_scallop.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZhouShirley_1998_submersible_study_red.md</t>
+  </si>
   <si>
     <t xml:space="preserve">AmbroseEtAl_2001_Role_echinoderms_benthic.md</t>
   </si>
@@ -25,31 +37,43 @@
     <t xml:space="preserve">AmbroseJr.EtAl_2005_subice_algal_community.md</t>
   </si>
   <si>
-    <t xml:space="preserve">AnsellEtAl_1998_Swimming_Antarctic_scallop.md</t>
+    <t xml:space="preserve">TeixidoEtAl_2006_Observations_asexual_reproductive.md</t>
   </si>
   <si>
-    <t xml:space="preserve">CastellanEtAl_2021_Visual_imaging_benthic.md</t>
+    <t xml:space="preserve">TeichertEtAl_2012_Rhodolith_beds_Corallinalesa.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GuttEtAl_2013_Shifts_Antarctic_megabenthic.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeichertEtAl_2014_Arctic_rhodolith_beds.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeichertFreiwald_2014_Polar_coralline_algal.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrookDavoren_2016_Influence_spawning_capelin.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YessonEtAl_2017_impact_trawling_epibenthic.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WatsonEtAl_2018_Patterns_distribution_abundance.md</t>
   </si>
   <si>
     <t xml:space="preserve">CooperEtAl_2019_video_seafloor_survey.md</t>
   </si>
   <si>
-    <t xml:space="preserve">CrookDavoren_2016_Influence_spawning_capelin.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DejaEtAl_2023_New_strategies_new.md</t>
-  </si>
-  <si>
     <t xml:space="preserve">DinnEtAl_2019_Sponge_Porifera_fauna.md</t>
   </si>
   <si>
-    <t xml:space="preserve">GuttEtAl_2013_Shifts_Antarctic_megabenthic.md</t>
+    <t xml:space="preserve">PierrejeanEtAl_2020_Influence_deepwater_corals.md</t>
   </si>
   <si>
-    <t xml:space="preserve">HamadaEtAl_1986_Observation_marine_benthic.md</t>
+    <t xml:space="preserve">WisshakNeumann_2020_Dead_urchin_walking.md</t>
   </si>
   <si>
-    <t xml:space="preserve">KimCazenave_2022_Benthic_community_descriptions.md</t>
+    <t xml:space="preserve">CastellanEtAl_2021_Visual_imaging_benthic.md</t>
   </si>
   <si>
     <t xml:space="preserve">KimEtAl_2021_Patterns_drivers_implications.md</t>
@@ -58,10 +82,13 @@
     <t xml:space="preserve">KrawczykEtAl_2021_First_highresolution_benthic.md</t>
   </si>
   <si>
-    <t xml:space="preserve">MedelyteEtAl_2022_Application_underwater_imagery.md</t>
+    <t xml:space="preserve">TeichertEtAl_2021_Microplastic_contamination_drilling.md</t>
   </si>
   <si>
-    <t xml:space="preserve">PierrejeanEtAl_2020_Influence_deepwater_corals.md</t>
+    <t xml:space="preserve">KimCazenave_2022_Benthic_community_descriptions.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MedelyteEtAl_2022_Application_underwater_imagery.md</t>
   </si>
   <si>
     <t xml:space="preserve">RangeleyEtAl_2022_Megabenthic_biodiversity_culturally.md</t>
@@ -73,37 +100,22 @@
     <t xml:space="preserve">SchimaniEtAl_2022_Video_survey_deep.md</t>
   </si>
   <si>
+    <t xml:space="preserve">WisshakEtAl_2022_Ten_Years_longterm.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DejaEtAl_2023_New_strategies_new.md</t>
+  </si>
+  <si>
     <t xml:space="preserve">SiglerEtAl_2023_Alaska_deepsea_coral.md</t>
   </si>
   <si>
-    <t xml:space="preserve">TeichertEtAl_2012_Rhodolith_beds_Corallinalesa.md</t>
+    <t xml:space="preserve">depth(transect(quadrat))</t>
   </si>
   <si>
-    <t xml:space="preserve">TeichertEtAl_2014_Arctic_rhodolith_beds.md</t>
+    <t xml:space="preserve">nd</t>
   </si>
   <si>
-    <t xml:space="preserve">TeichertEtAl_2021_Microplastic_contamination_drilling.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeichertFreiwald_2014_Polar_coralline_algal.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeixidoEtAl_2006_Observations_asexual_reproductive.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WatsonEtAl_2018_Patterns_distribution_abundance.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WisshakEtAl_2022_Ten_Years_longterm.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WisshakNeumann_2020_Dead_urchin_walking.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YessonEtAl_2017_impact_trawling_epibenthic.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZhouShirley_1998_submersible_study_red.md</t>
+    <t xml:space="preserve">site(transect)</t>
   </si>
   <si>
     <t xml:space="preserve">site(transect(depth))</t>
@@ -112,34 +124,28 @@
     <t xml:space="preserve">site(transect(quadrat))</t>
   </si>
   <si>
-    <t xml:space="preserve">nd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">site(transect)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">site(stationary)</t>
+    <t xml:space="preserve">site(depth(transect))</t>
   </si>
   <si>
     <t xml:space="preserve">site(transect(depth(sample)))</t>
   </si>
   <si>
-    <t xml:space="preserve">site(transect(depth(quadrat)))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">site(depth(transect))</t>
+    <t xml:space="preserve">site(depth(sample))</t>
   </si>
   <si>
     <t xml:space="preserve">site(sample)</t>
   </si>
   <si>
+    <t xml:space="preserve">stationary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">site(transect(depth(quadrat)))</t>
+  </si>
+  <si>
     <t xml:space="preserve">transect(sample)</t>
   </si>
   <si>
-    <t xml:space="preserve">site(depth(sample))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stationary</t>
+    <t xml:space="preserve">site(stationary)</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
@@ -154,37 +160,22 @@
     <t xml:space="preserve">ex</t>
   </si>
   <si>
+    <t xml:space="preserve">slope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temperature</t>
+  </si>
+  <si>
     <t xml:space="preserve">chl</t>
   </si>
   <si>
     <t xml:space="preserve">salinity</t>
   </si>
   <si>
-    <t xml:space="preserve">temperature</t>
-  </si>
-  <si>
     <t xml:space="preserve">sediment</t>
   </si>
   <si>
     <t xml:space="preserve">water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nutrient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tide</t>
   </si>
   <si>
     <t xml:space="preserve">co2</t>
@@ -196,7 +187,22 @@
     <t xml:space="preserve">light</t>
   </si>
   <si>
+    <t xml:space="preserve">nutrient</t>
+  </si>
+  <si>
     <t xml:space="preserve">ph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tide</t>
   </si>
 </sst>
 </file>
@@ -613,6 +619,9 @@
       <c r="AC1" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -702,6 +711,9 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -791,6 +803,9 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -880,6 +895,9 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -969,6 +987,9 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1058,6 +1079,9 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1147,6 +1171,9 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1236,6 +1263,9 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1325,6 +1355,9 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1414,6 +1447,9 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1503,6 +1539,9 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1592,6 +1631,9 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1681,6 +1723,9 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1770,6 +1815,9 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1859,6 +1907,9 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1948,6 +1999,9 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2037,6 +2091,9 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2126,6 +2183,9 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2215,6 +2275,9 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2304,6 +2367,9 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2393,6 +2459,9 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2482,6 +2551,9 @@
       <c r="AC22" t="n">
         <v>0</v>
       </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2571,6 +2643,9 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2660,6 +2735,9 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2749,6 +2827,9 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2838,6 +2919,9 @@
       <c r="AC26" t="n">
         <v>0</v>
       </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2927,6 +3011,9 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3016,6 +3103,9 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3105,6 +3195,9 @@
       <c r="AC29" t="n">
         <v>0</v>
       </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3192,6 +3285,101 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3208,40 +3396,43 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L1" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="M1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2">
@@ -3281,6 +3472,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3319,16 +3513,19 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3355,6 +3552,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3395,6 +3595,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3433,6 +3636,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3445,10 +3651,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3469,6 +3675,9 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3486,10 +3695,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -3507,7 +3716,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3527,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -3545,6 +3757,9 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3556,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3583,6 +3798,9 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3623,6 +3841,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3635,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -3647,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3659,6 +3880,9 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3670,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -3682,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -3697,6 +3921,9 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3714,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -3723,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3735,6 +3962,9 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3775,6 +4005,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3784,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3802,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -3811,6 +4044,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3851,6 +4087,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3878,21 +4117,24 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -3919,12 +4161,15 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3933,13 +4178,13 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -3963,6 +4208,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3983,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3998,9 +4246,12 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4015,13 +4266,13 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -4039,6 +4290,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4065,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -4074,9 +4328,12 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4088,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -4112,9 +4369,12 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4126,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -4141,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -4153,12 +4413,15 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -4188,9 +4451,12 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4220,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -4229,6 +4495,9 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4243,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -4267,7 +4536,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4275,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -4296,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4305,6 +4577,9 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4319,7 +4594,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -4337,12 +4612,56 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4359,10 +4678,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -4375,10 +4694,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -4439,10 +4758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4594,6 +4913,14 @@
         <v>1</v>
       </c>
       <c r="B30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4610,10 +4937,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -4666,10 +4993,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4698,10 +5025,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4714,10 +5041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -4754,10 +5081,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -4794,10 +5121,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4818,18 +5145,18 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4842,9 +5169,17 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4861,13 +5196,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
@@ -4883,10 +5218,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -4905,10 +5240,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -4916,10 +5251,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -4927,10 +5262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -4938,10 +5273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4971,10 +5306,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -4993,10 +5328,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -5004,13 +5339,13 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5026,10 +5361,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -5037,10 +5372,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -5048,10 +5383,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -5070,13 +5405,13 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5147,10 +5482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -5169,13 +5504,13 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -5187,6 +5522,17 @@
       </c>
       <c r="C30" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5202,52 +5548,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
@@ -5258,7 +5604,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -5305,16 +5651,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -5358,7 +5704,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -5367,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -5405,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -5417,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -5455,19 +5801,19 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -5505,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -5514,13 +5860,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -5555,7 +5901,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -5608,13 +5954,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5623,25 +5969,25 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5658,13 +6004,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5705,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -5714,10 +6060,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -5726,16 +6072,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -5758,7 +6104,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -5767,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -5805,13 +6151,13 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5820,10 +6166,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -5855,13 +6201,13 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -5888,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -5908,7 +6254,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -5917,7 +6263,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5952,16 +6298,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -5970,13 +6316,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -6005,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -6014,10 +6360,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -6061,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -6082,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -6091,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -6108,7 +6454,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6117,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -6152,7 +6498,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -6179,13 +6525,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -6208,46 +6554,46 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -6255,10 +6601,10 @@
         <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -6267,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -6291,13 +6637,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -6308,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -6317,7 +6663,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -6358,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -6367,7 +6713,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -6408,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -6417,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -6458,7 +6804,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -6467,7 +6813,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -6505,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -6558,7 +6904,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -6567,7 +6913,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -6605,16 +6951,16 @@
         <v>0</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -6629,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -6655,16 +7001,16 @@
         <v>0</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -6698,6 +7044,56 @@
       </c>
       <c r="P30" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
